--- a/research/traditional_assets/database/data/switzerland/switzerland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_financial_svcs_non_bank_insurance.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03695</v>
+        <v>0.0444</v>
       </c>
       <c r="E2">
-        <v>0.0254</v>
+        <v>0.0418</v>
       </c>
       <c r="F2">
-        <v>0.00523</v>
+        <v>0.03823</v>
       </c>
       <c r="G2">
-        <v>0.0003247621774083791</v>
+        <v>0.0002758013081409268</v>
       </c>
       <c r="H2">
-        <v>0.0003247621774083791</v>
+        <v>0.0002758013081409268</v>
       </c>
       <c r="I2">
-        <v>-0.001673009943774207</v>
+        <v>-0.001160222491071674</v>
       </c>
       <c r="J2">
-        <v>-0.00138246405247764</v>
+        <v>-0.001046666328096737</v>
       </c>
       <c r="K2">
-        <v>58620.26</v>
+        <v>-615.97</v>
       </c>
       <c r="L2">
-        <v>0.5502209039839684</v>
+        <v>-0.01179759248441435</v>
       </c>
       <c r="M2">
-        <v>31617.931</v>
+        <v>23250.3488</v>
       </c>
       <c r="N2">
-        <v>0.3585181527282953</v>
+        <v>0.3125559406246723</v>
       </c>
       <c r="O2">
-        <v>0.5393686585491091</v>
+        <v>-37.7459110021592</v>
       </c>
       <c r="P2">
-        <v>3387.378</v>
+        <v>2080.7988</v>
       </c>
       <c r="Q2">
-        <v>0.03840973981354022</v>
+        <v>0.02797231266417343</v>
       </c>
       <c r="R2">
-        <v>0.05778510706025528</v>
+        <v>-3.37808464697956</v>
       </c>
       <c r="S2">
-        <v>28230.553</v>
+        <v>21169.55</v>
       </c>
       <c r="T2">
-        <v>0.8928652858404935</v>
+        <v>0.9105046200425173</v>
       </c>
       <c r="U2">
-        <v>363038</v>
+        <v>332037.6</v>
       </c>
       <c r="V2">
-        <v>4.116515819146258</v>
+        <v>4.463602902626506</v>
       </c>
       <c r="W2">
-        <v>0.08363931694533479</v>
+        <v>0.03222435115833478</v>
       </c>
       <c r="X2">
-        <v>0.05906172388949673</v>
+        <v>0.09582769545409243</v>
       </c>
       <c r="Y2">
-        <v>0.02457759305583806</v>
+        <v>-0.06360334429575765</v>
       </c>
       <c r="Z2">
-        <v>0.1758679228577143</v>
+        <v>0.08640582002481546</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02679236219551766</v>
+        <v>0.0486625033160148</v>
       </c>
       <c r="AC2">
-        <v>-0.02664323384810744</v>
+        <v>-0.04833932548008228</v>
       </c>
       <c r="AD2">
-        <v>625114.6</v>
+        <v>709550.6</v>
       </c>
       <c r="AE2">
-        <v>3196.558214523661</v>
+        <v>2491.884782962944</v>
       </c>
       <c r="AF2">
-        <v>628311.1582145237</v>
+        <v>712042.4847829629</v>
       </c>
       <c r="AG2">
-        <v>265273.1582145237</v>
+        <v>380004.884782963</v>
       </c>
       <c r="AH2">
-        <v>0.8769150263918887</v>
+        <v>0.9054108146146364</v>
       </c>
       <c r="AI2">
-        <v>0.645227833024701</v>
+        <v>0.8172890592872022</v>
       </c>
       <c r="AJ2">
-        <v>0.7504960609102236</v>
+        <v>0.8362918187480709</v>
       </c>
       <c r="AK2">
-        <v>0.4343443730896211</v>
+        <v>0.7047735842162586</v>
       </c>
       <c r="AL2">
-        <v>18.8</v>
+        <v>28.1</v>
       </c>
       <c r="AM2">
-        <v>18.8</v>
+        <v>26.71</v>
       </c>
       <c r="AN2">
-        <v>1355.203243219806</v>
+        <v>1620.718592964824</v>
       </c>
       <c r="AO2">
-        <v>1</v>
+        <v>0.7259786476868326</v>
       </c>
       <c r="AP2">
-        <v>575.0930219058766</v>
+        <v>867.9874024279648</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.7637588918008236</v>
       </c>
     </row>
     <row r="3">
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0583</v>
+        <v>0.119</v>
       </c>
       <c r="G3">
-        <v>1.071207430340557</v>
+        <v>0.4472049689440993</v>
       </c>
       <c r="H3">
-        <v>1.071207430340557</v>
+        <v>0.4472049689440993</v>
       </c>
       <c r="I3">
-        <v>0.5820433436532508</v>
+        <v>0.6335403726708073</v>
       </c>
       <c r="J3">
-        <v>0.5820433436532508</v>
+        <v>0.6335403726708073</v>
       </c>
       <c r="K3">
-        <v>-2.44</v>
+        <v>-5.07</v>
       </c>
       <c r="L3">
-        <v>-0.07554179566563468</v>
+        <v>-0.1574534161490683</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,73 +767,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>113.7</v>
+        <v>56.7</v>
       </c>
       <c r="V3">
-        <v>2.477124183006536</v>
+        <v>1.56198347107438</v>
       </c>
       <c r="W3">
-        <v>-0.0548314606741573</v>
+        <v>-0.1190140845070423</v>
       </c>
       <c r="X3">
-        <v>0.05681931410149258</v>
+        <v>0.09121559213514113</v>
       </c>
       <c r="Y3">
-        <v>-0.1116507747756499</v>
+        <v>-0.2102296766421834</v>
       </c>
       <c r="Z3">
-        <v>0.1820538834404238</v>
+        <v>0.2047304170905392</v>
       </c>
       <c r="AA3">
-        <v>0.1059632510427235</v>
+        <v>0.12970498474059</v>
       </c>
       <c r="AB3">
-        <v>0.02593867429335162</v>
+        <v>0.04669620030966593</v>
       </c>
       <c r="AC3">
-        <v>0.08002457674937186</v>
+        <v>0.08300878443092408</v>
       </c>
       <c r="AD3">
-        <v>233.2</v>
+        <v>204.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>233.2</v>
+        <v>204.3</v>
       </c>
       <c r="AG3">
-        <v>119.5</v>
+        <v>147.6</v>
       </c>
       <c r="AH3">
-        <v>0.8355428161949123</v>
+        <v>0.8491271820448878</v>
       </c>
       <c r="AI3">
-        <v>0.8455402465554749</v>
+        <v>0.8689919183326243</v>
       </c>
       <c r="AJ3">
-        <v>0.722490931076179</v>
+        <v>0.8026101141924959</v>
       </c>
       <c r="AK3">
-        <v>0.7371992597162245</v>
+        <v>0.827354260089686</v>
       </c>
       <c r="AL3">
-        <v>18.8</v>
+        <v>28.1</v>
       </c>
       <c r="AM3">
-        <v>18.8</v>
+        <v>26.71</v>
       </c>
       <c r="AN3">
-        <v>12.27368421052632</v>
+        <v>10.01470588235294</v>
       </c>
       <c r="AO3">
-        <v>1</v>
+        <v>0.7259786476868326</v>
       </c>
       <c r="AP3">
-        <v>6.289473684210526</v>
+        <v>7.235294117647061</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.7637588918008236</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hypothekarbank Lenzburg AG (SWX:HBLN)</t>
+          <t>Schweizerische Nationalbank (SWX:SNBN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,47 +852,17 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0373</v>
-      </c>
-      <c r="E4">
-        <v>-0.0332</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>20.3</v>
-      </c>
-      <c r="L4">
-        <v>0.2159574468085106</v>
-      </c>
       <c r="M4">
-        <v>8.568</v>
+        <v>1.53</v>
       </c>
       <c r="N4">
-        <v>0.0258305697919807</v>
-      </c>
-      <c r="O4">
-        <v>0.4220689655172413</v>
+        <v>0.002953667953667954</v>
       </c>
       <c r="P4">
-        <v>8.568</v>
+        <v>1.53</v>
       </c>
       <c r="Q4">
-        <v>0.0258305697919807</v>
-      </c>
-      <c r="R4">
-        <v>0.4220689655172413</v>
+        <v>0.002953667953667954</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,55 +871,49 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1411.1</v>
+        <v>11705.6</v>
       </c>
       <c r="V4">
-        <v>4.254145312028942</v>
-      </c>
-      <c r="W4">
-        <v>0.03700328107911046</v>
+        <v>22.5976833976834</v>
       </c>
       <c r="X4">
-        <v>0.05032287113182307</v>
-      </c>
-      <c r="Y4">
-        <v>-0.01331959005271261</v>
+        <v>1.217768046955018</v>
       </c>
       <c r="Z4">
-        <v>0.1034672537149147</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02582603333339808</v>
+        <v>0.04645159641320681</v>
       </c>
       <c r="AC4">
-        <v>-0.02582603333339808</v>
+        <v>-0.04645159641320681</v>
       </c>
       <c r="AD4">
-        <v>1362.1</v>
+        <v>79151.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1362.1</v>
+        <v>79151.3</v>
       </c>
       <c r="AG4">
-        <v>-49</v>
+        <v>67445.7</v>
       </c>
       <c r="AH4">
-        <v>0.8041681426378556</v>
+        <v>0.9934981228653949</v>
       </c>
       <c r="AI4">
-        <v>0.7034913748579692</v>
+        <v>0.5816253497777882</v>
       </c>
       <c r="AJ4">
-        <v>-0.1733286169083834</v>
+        <v>0.992378284289996</v>
       </c>
       <c r="AK4">
-        <v>-0.09331555894115406</v>
+        <v>0.5422516980112686</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -966,7 +930,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Schweizerische Nationalbank (SWX:SNBN)</t>
+          <t>Hypothekarbank Lenzburg AG (SWX:HBLN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,10 +939,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0366</v>
+        <v>0.0444</v>
       </c>
       <c r="E5">
-        <v>0.0372</v>
+        <v>-0.0329</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -993,28 +957,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>50599.1</v>
+        <v>18.5</v>
       </c>
       <c r="L5">
-        <v>0.9917755646459043</v>
+        <v>0.1887755102040816</v>
       </c>
       <c r="M5">
-        <v>1.61</v>
+        <v>8.668799999999999</v>
       </c>
       <c r="N5">
-        <v>0.002808792742498256</v>
+        <v>0.02719196988707653</v>
       </c>
       <c r="O5">
-        <v>3.181874776428831e-05</v>
+        <v>0.4685837837837837</v>
       </c>
       <c r="P5">
-        <v>1.61</v>
+        <v>8.668799999999999</v>
       </c>
       <c r="Q5">
-        <v>0.002808792742498256</v>
+        <v>0.02719196988707653</v>
       </c>
       <c r="R5">
-        <v>3.181874776428831e-05</v>
+        <v>0.4685837837837837</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,55 +987,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>12714.7</v>
+        <v>1348.3</v>
       </c>
       <c r="V5">
-        <v>22.18196092114445</v>
+        <v>4.229297365119197</v>
       </c>
       <c r="W5">
-        <v>0.2605227848218579</v>
+        <v>0.03222435115833478</v>
       </c>
       <c r="X5">
-        <v>0.2217243807761086</v>
+        <v>0.07732934722679684</v>
       </c>
       <c r="Y5">
-        <v>0.03879840404574933</v>
+        <v>-0.04510499606846206</v>
       </c>
       <c r="Z5">
-        <v>0.2682225936240045</v>
+        <v>0.1866311178823082</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02641257713284164</v>
+        <v>0.04679252837421179</v>
       </c>
       <c r="AC5">
-        <v>-0.02641257713284164</v>
+        <v>-0.04679252837421179</v>
       </c>
       <c r="AD5">
-        <v>17086.7</v>
+        <v>1215.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>17086.7</v>
+        <v>1215.9</v>
       </c>
       <c r="AG5">
-        <v>4372</v>
+        <v>-132.3999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.9675422850639018</v>
+        <v>0.7922721052974523</v>
       </c>
       <c r="AI5">
-        <v>0.06775416784469601</v>
+        <v>0.6819023049744827</v>
       </c>
       <c r="AJ5">
-        <v>0.8840896222599693</v>
+        <v>-0.7103004291845481</v>
       </c>
       <c r="AK5">
-        <v>0.01825683169639875</v>
+        <v>-0.3045078196872121</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1097,13 +1061,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0476</v>
+        <v>0.0594</v>
       </c>
       <c r="E6">
-        <v>0.0136</v>
+        <v>0.0418</v>
       </c>
       <c r="F6">
-        <v>0.00523</v>
+        <v>0.00666</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,91 +1076,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.002396890382602016</v>
+        <v>0.005287510874248636</v>
       </c>
       <c r="J6">
-        <v>0.001916612488012123</v>
+        <v>0.004243093127545525</v>
       </c>
       <c r="K6">
-        <v>170.4</v>
+        <v>181.6</v>
       </c>
       <c r="L6">
-        <v>0.3555184644272898</v>
+        <v>0.3767634854771784</v>
       </c>
       <c r="M6">
-        <v>119.753</v>
+        <v>121.45</v>
       </c>
       <c r="N6">
-        <v>0.0560798913552496</v>
+        <v>0.04976847108962013</v>
       </c>
       <c r="O6">
-        <v>0.7027758215962441</v>
+        <v>0.6687775330396476</v>
       </c>
       <c r="P6">
-        <v>119.2</v>
+        <v>118.3</v>
       </c>
       <c r="Q6">
-        <v>0.05582092348037838</v>
+        <v>0.04847764619104208</v>
       </c>
       <c r="R6">
-        <v>0.6995305164319249</v>
+        <v>0.651431718061674</v>
       </c>
       <c r="S6">
-        <v>0.5529999999999973</v>
+        <v>3.150000000000006</v>
       </c>
       <c r="T6">
-        <v>0.004617838384007059</v>
+        <v>0.02593659942363117</v>
       </c>
       <c r="U6">
-        <v>598.2</v>
+        <v>508.7</v>
       </c>
       <c r="V6">
-        <v>0.2801348693453217</v>
+        <v>0.2084579764783018</v>
       </c>
       <c r="W6">
-        <v>0.1530035018407112</v>
+        <v>0.1529520761391392</v>
       </c>
       <c r="X6">
-        <v>0.03153150338723699</v>
+        <v>0.0563940630796783</v>
       </c>
       <c r="Y6">
-        <v>0.1214719984534742</v>
+        <v>0.09655801305946092</v>
       </c>
       <c r="Z6">
-        <v>0.1556165874353583</v>
+        <v>0.1523312480862137</v>
       </c>
       <c r="AA6">
-        <v>0.0002982566948204381</v>
+        <v>0.0006463556718650458</v>
       </c>
       <c r="AB6">
-        <v>0.02717214725819368</v>
+        <v>0.05053247825781781</v>
       </c>
       <c r="AC6">
-        <v>-0.02687389056337324</v>
+        <v>-0.04988612258595277</v>
       </c>
       <c r="AD6">
-        <v>2721.9</v>
+        <v>2610.3</v>
       </c>
       <c r="AE6">
-        <v>29.60585219809427</v>
+        <v>22.75709879306078</v>
       </c>
       <c r="AF6">
-        <v>2751.505852198095</v>
+        <v>2633.057098793061</v>
       </c>
       <c r="AG6">
-        <v>2153.305852198095</v>
+        <v>2124.357098793061</v>
       </c>
       <c r="AH6">
-        <v>0.5630363946873433</v>
+        <v>0.518996996962713</v>
       </c>
       <c r="AI6">
-        <v>0.6985634619849531</v>
+        <v>0.6813523947815107</v>
       </c>
       <c r="AJ6">
-        <v>0.5020875589064843</v>
+        <v>0.4653924824615548</v>
       </c>
       <c r="AK6">
-        <v>0.6445854277544401</v>
+        <v>0.6330485301087829</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1205,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>384.992927864215</v>
+        <v>367.6478873239437</v>
       </c>
       <c r="AP6">
-        <v>304.5694274679059</v>
+        <v>299.2052251821213</v>
       </c>
     </row>
     <row r="7">
@@ -1228,13 +1192,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0305</v>
+        <v>0.0356</v>
       </c>
       <c r="E7">
-        <v>0.155</v>
+        <v>0.123</v>
       </c>
       <c r="F7">
-        <v>0.118</v>
+        <v>0.0698</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1249,85 +1213,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>7745</v>
+        <v>7325</v>
       </c>
       <c r="L7">
-        <v>0.2217672660634521</v>
+        <v>0.2080729462561073</v>
       </c>
       <c r="M7">
-        <v>5610</v>
+        <v>7243</v>
       </c>
       <c r="N7">
-        <v>0.09064644976150774</v>
+        <v>0.1223213184964763</v>
       </c>
       <c r="O7">
-        <v>0.724338282763073</v>
+        <v>0.9888054607508533</v>
       </c>
       <c r="P7">
-        <v>2600</v>
+        <v>1668</v>
       </c>
       <c r="Q7">
-        <v>0.04201083233153656</v>
+        <v>0.02816953738121254</v>
       </c>
       <c r="R7">
-        <v>0.3357004519044545</v>
+        <v>0.2277133105802048</v>
       </c>
       <c r="S7">
-        <v>3010</v>
+        <v>5575</v>
       </c>
       <c r="T7">
-        <v>0.5365418894830659</v>
+        <v>0.769708684246859</v>
       </c>
       <c r="U7">
-        <v>185571</v>
+        <v>166406</v>
       </c>
       <c r="V7">
-        <v>2.998458525613681</v>
+        <v>2.810299782648713</v>
       </c>
       <c r="W7">
-        <v>0.1302753528115591</v>
+        <v>0.1216393497069031</v>
       </c>
       <c r="X7">
-        <v>0.06130413367750088</v>
+        <v>0.1004397987730437</v>
       </c>
       <c r="Y7">
-        <v>0.06897121913405824</v>
+        <v>0.0211995509338594</v>
       </c>
       <c r="Z7">
-        <v>0.1341466225196088</v>
+        <v>0.1525944612770532</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0293441444675688</v>
+        <v>0.05216481483763205</v>
       </c>
       <c r="AC7">
-        <v>-0.0293441444675688</v>
+        <v>-0.05216481483763205</v>
       </c>
       <c r="AD7">
-        <v>356055</v>
+        <v>404611</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>356055</v>
+        <v>404611</v>
       </c>
       <c r="AG7">
-        <v>170484</v>
+        <v>238205</v>
       </c>
       <c r="AH7">
-        <v>0.8519207606381528</v>
+        <v>0.8723375401741911</v>
       </c>
       <c r="AI7">
-        <v>0.854654386508148</v>
+        <v>0.8782583780662778</v>
       </c>
       <c r="AJ7">
-        <v>0.7336659023775589</v>
+        <v>0.8009100998964755</v>
       </c>
       <c r="AK7">
-        <v>0.7379109749130006</v>
+        <v>0.809419927894499</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1353,10 +1317,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.00353</v>
-      </c>
-      <c r="F8">
-        <v>-0.0635</v>
+        <v>-0.0474</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1365,91 +1326,91 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-0.009913885732978174</v>
+        <v>-0.005094480542227136</v>
       </c>
       <c r="J8">
-        <v>-0.004956942866489087</v>
+        <v>-0.005094480542227136</v>
       </c>
       <c r="K8">
-        <v>87.90000000000001</v>
+        <v>-8136</v>
       </c>
       <c r="L8">
-        <v>0.004396934651246549</v>
+        <v>-0.4962397760333754</v>
       </c>
       <c r="M8">
-        <v>25878</v>
+        <v>15875.7</v>
       </c>
       <c r="N8">
-        <v>1.114681507262358</v>
+        <v>1.338422627829532</v>
       </c>
       <c r="O8">
-        <v>294.4027303754266</v>
+        <v>-1.951290560471976</v>
       </c>
       <c r="P8">
-        <v>658</v>
+        <v>284.3</v>
       </c>
       <c r="Q8">
-        <v>0.02834301073416151</v>
+        <v>0.02396830080512583</v>
       </c>
       <c r="R8">
-        <v>7.485779294653014</v>
+        <v>-0.03494346116027532</v>
       </c>
       <c r="S8">
-        <v>25220</v>
+        <v>15591.4</v>
       </c>
       <c r="T8">
-        <v>0.9745729963675709</v>
+        <v>0.9820921282211178</v>
       </c>
       <c r="U8">
-        <v>162629.3</v>
+        <v>152012.3</v>
       </c>
       <c r="V8">
-        <v>7.00517324557625</v>
+        <v>12.81560510896598</v>
       </c>
       <c r="W8">
-        <v>0.001762823083957709</v>
+        <v>-0.1706096737530353</v>
       </c>
       <c r="X8">
-        <v>0.09498650761084421</v>
+        <v>0.1928351920925972</v>
       </c>
       <c r="Y8">
-        <v>-0.09322368452688649</v>
+        <v>-0.3634448658456325</v>
       </c>
       <c r="Z8">
-        <v>0.132326807659409</v>
+        <v>0.1258876783945033</v>
       </c>
       <c r="AA8">
-        <v>-0.0006559364252725809</v>
+        <v>-0.0006413323280869444</v>
       </c>
       <c r="AB8">
-        <v>0.03070511600904463</v>
+        <v>0.05711740756619302</v>
       </c>
       <c r="AC8">
-        <v>-0.03136105243431721</v>
+        <v>-0.05775873989427996</v>
       </c>
       <c r="AD8">
-        <v>247655.7</v>
+        <v>221757.8</v>
       </c>
       <c r="AE8">
-        <v>3166.952362325566</v>
+        <v>2469.127684169883</v>
       </c>
       <c r="AF8">
-        <v>250822.6523623256</v>
+        <v>224226.9276841699</v>
       </c>
       <c r="AG8">
-        <v>88193.35236232559</v>
+        <v>72214.62768416989</v>
       </c>
       <c r="AH8">
-        <v>0.9152833598963952</v>
+        <v>0.9497582320474095</v>
       </c>
       <c r="AI8">
-        <v>0.8393283181622337</v>
+        <v>0.8349269808422125</v>
       </c>
       <c r="AJ8">
-        <v>0.7916181823117954</v>
+        <v>0.8589195253549561</v>
       </c>
       <c r="AK8">
-        <v>0.6474900039516268</v>
+        <v>0.6196211168296372</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1458,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>569.0618106617648</v>
+        <v>540.4772117962466</v>
       </c>
       <c r="AP8">
-        <v>202.6501662737261</v>
+        <v>176.0044545068727</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0444</v>
+        <v>0.01035</v>
       </c>
       <c r="E2">
-        <v>0.0418</v>
+        <v>0.183665</v>
       </c>
       <c r="F2">
-        <v>0.03823</v>
+        <v>0.04485</v>
       </c>
       <c r="G2">
-        <v>0.0002758013081409268</v>
+        <v>0.00202358768814873</v>
       </c>
       <c r="H2">
-        <v>0.0002758013081409268</v>
+        <v>0.001496204796449737</v>
       </c>
       <c r="I2">
-        <v>-0.001160222491071674</v>
+        <v>0.0020323652797033</v>
       </c>
       <c r="J2">
-        <v>-0.001046666328096737</v>
+        <v>0.001633143507512428</v>
       </c>
       <c r="K2">
-        <v>-615.97</v>
+        <v>43736.47</v>
       </c>
       <c r="L2">
-        <v>-0.01179759248441435</v>
+        <v>0.8542913341224545</v>
       </c>
       <c r="M2">
-        <v>23250.3488</v>
+        <v>5178.25</v>
       </c>
       <c r="N2">
-        <v>0.3125559406246723</v>
+        <v>0.04963851333215746</v>
       </c>
       <c r="O2">
-        <v>-37.7459110021592</v>
+        <v>0.1183966149988785</v>
       </c>
       <c r="P2">
-        <v>2080.7988</v>
+        <v>1816.05</v>
       </c>
       <c r="Q2">
-        <v>0.02797231266417343</v>
+        <v>0.01740858825604491</v>
       </c>
       <c r="R2">
-        <v>-3.37808464697956</v>
+        <v>0.04152255543257149</v>
       </c>
       <c r="S2">
-        <v>21169.55</v>
+        <v>3362.2</v>
       </c>
       <c r="T2">
-        <v>0.9105046200425173</v>
+        <v>0.649292714720224</v>
       </c>
       <c r="U2">
-        <v>332037.6</v>
+        <v>294541.2</v>
       </c>
       <c r="V2">
-        <v>4.463602902626506</v>
+        <v>2.823461069486729</v>
       </c>
       <c r="W2">
-        <v>0.03222435115833478</v>
+        <v>0.1395159980509989</v>
       </c>
       <c r="X2">
-        <v>0.09582769545409243</v>
+        <v>0.06407590061507314</v>
       </c>
       <c r="Y2">
-        <v>-0.06360334429575765</v>
+        <v>0.07544009743592574</v>
       </c>
       <c r="Z2">
-        <v>0.08640582002481546</v>
+        <v>0.1213952959654896</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.0006510883691224188</v>
       </c>
       <c r="AB2">
-        <v>0.0486625033160148</v>
+        <v>0.0516375942599599</v>
       </c>
       <c r="AC2">
-        <v>-0.04833932548008228</v>
+        <v>-0.04788036930927565</v>
       </c>
       <c r="AD2">
-        <v>709550.6</v>
+        <v>851443.9</v>
       </c>
       <c r="AE2">
-        <v>2491.884782962944</v>
+        <v>52.95310333626954</v>
       </c>
       <c r="AF2">
-        <v>712042.4847829629</v>
+        <v>851496.8531033363</v>
       </c>
       <c r="AG2">
-        <v>380004.884782963</v>
+        <v>556955.6531033362</v>
       </c>
       <c r="AH2">
-        <v>0.9054108146146364</v>
+        <v>0.8908584976562204</v>
       </c>
       <c r="AI2">
-        <v>0.8172890592872022</v>
+        <v>0.8412884461646618</v>
       </c>
       <c r="AJ2">
-        <v>0.8362918187480709</v>
+        <v>0.8422453242998216</v>
       </c>
       <c r="AK2">
-        <v>0.7047735842162586</v>
+        <v>0.7761441539807276</v>
       </c>
       <c r="AL2">
-        <v>28.1</v>
+        <v>45.9</v>
       </c>
       <c r="AM2">
-        <v>26.71</v>
+        <v>41.384</v>
       </c>
       <c r="AN2">
-        <v>1620.718592964824</v>
+        <v>6300.458043510434</v>
       </c>
       <c r="AO2">
-        <v>0.7259786476868326</v>
+        <v>2.167755991285403</v>
       </c>
       <c r="AP2">
-        <v>867.9874024279648</v>
+        <v>4121.323465319937</v>
       </c>
       <c r="AQ2">
-        <v>0.7637588918008236</v>
+        <v>2.404310844770926</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DDM Holding AG (OM:DDM)</t>
+          <t>Global Blue Group Holding AG (NYSE:GB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,26 +724,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.119</v>
-      </c>
       <c r="G3">
-        <v>0.4472049689440993</v>
+        <v>0.1923648983639068</v>
       </c>
       <c r="H3">
-        <v>0.4472049689440993</v>
+        <v>0.1254338125929599</v>
       </c>
       <c r="I3">
-        <v>0.6335403726708073</v>
+        <v>0.2126921170054537</v>
       </c>
       <c r="J3">
-        <v>0.6335403726708073</v>
+        <v>0.1063460585027268</v>
       </c>
       <c r="K3">
-        <v>-5.07</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.1574534161490683</v>
+        <v>0.0236737729300942</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -761,79 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>56.7</v>
+        <v>234.6</v>
       </c>
       <c r="V3">
-        <v>1.56198347107438</v>
+        <v>0.2072804382399717</v>
       </c>
       <c r="W3">
-        <v>-0.1190140845070423</v>
+        <v>-7.701612903225807</v>
       </c>
       <c r="X3">
-        <v>0.09121559213514113</v>
+        <v>0.05678260670064698</v>
       </c>
       <c r="Y3">
-        <v>-0.2102296766421834</v>
+        <v>-7.758395509926454</v>
       </c>
       <c r="Z3">
-        <v>0.2047304170905392</v>
+        <v>4.160478547854784</v>
       </c>
       <c r="AA3">
-        <v>0.12970498474059</v>
+        <v>0.4424504950495048</v>
       </c>
       <c r="AB3">
-        <v>0.04669620030966593</v>
+        <v>0.05812924957302749</v>
       </c>
       <c r="AC3">
-        <v>0.08300878443092408</v>
+        <v>0.3843212454764773</v>
       </c>
       <c r="AD3">
-        <v>204.3</v>
+        <v>837.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>204.3</v>
+        <v>837.9</v>
       </c>
       <c r="AG3">
-        <v>147.6</v>
+        <v>603.3</v>
       </c>
       <c r="AH3">
-        <v>0.8491271820448878</v>
+        <v>0.4253947301619536</v>
       </c>
       <c r="AI3">
-        <v>0.8689919183326243</v>
+        <v>0.9782837127845884</v>
       </c>
       <c r="AJ3">
-        <v>0.8026101141924959</v>
+        <v>0.3477033024033197</v>
       </c>
       <c r="AK3">
-        <v>0.827354260089686</v>
+        <v>0.97009165460685</v>
       </c>
       <c r="AL3">
-        <v>28.1</v>
+        <v>45.9</v>
       </c>
       <c r="AM3">
-        <v>26.71</v>
+        <v>41.98</v>
       </c>
       <c r="AN3">
-        <v>10.01470588235294</v>
+        <v>8.82</v>
       </c>
       <c r="AO3">
-        <v>0.7259786476868326</v>
+        <v>1.869281045751634</v>
       </c>
       <c r="AP3">
-        <v>7.235294117647061</v>
+        <v>6.350526315789473</v>
       </c>
       <c r="AQ3">
-        <v>0.7637588918008236</v>
+        <v>2.043830395426394</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Schweizerische Nationalbank (SWX:SNBN)</t>
+          <t>Orell Füssli AG (SWX:OFN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,17 +849,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0459</v>
+      </c>
+      <c r="E4">
+        <v>0.366</v>
+      </c>
+      <c r="G4">
+        <v>0.1035444046196734</v>
+      </c>
+      <c r="H4">
+        <v>0.1035444046196734</v>
+      </c>
+      <c r="I4">
+        <v>0.06241058212722968</v>
+      </c>
+      <c r="J4">
+        <v>0.04760420953980415</v>
+      </c>
+      <c r="K4">
+        <v>7.42</v>
+      </c>
+      <c r="L4">
+        <v>0.0295499800876145</v>
+      </c>
       <c r="M4">
-        <v>1.53</v>
+        <v>7.45</v>
       </c>
       <c r="N4">
-        <v>0.002953667953667954</v>
+        <v>0.04257142857142857</v>
+      </c>
+      <c r="O4">
+        <v>1.004043126684636</v>
       </c>
       <c r="P4">
-        <v>1.53</v>
+        <v>7.45</v>
       </c>
       <c r="Q4">
-        <v>0.002953667953667954</v>
+        <v>0.04257142857142857</v>
+      </c>
+      <c r="R4">
+        <v>1.004043126684636</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -871,55 +898,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>11705.6</v>
+        <v>46.4</v>
       </c>
       <c r="V4">
-        <v>22.5976833976834</v>
+        <v>0.2651428571428571</v>
+      </c>
+      <c r="W4">
+        <v>0.05638297872340426</v>
       </c>
       <c r="X4">
-        <v>1.217768046955018</v>
+        <v>0.05180605746985757</v>
+      </c>
+      <c r="Y4">
+        <v>0.004576921253546695</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.395683438934884</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.1140446164180948</v>
       </c>
       <c r="AB4">
-        <v>0.04645159641320681</v>
+        <v>0.04947830278681391</v>
       </c>
       <c r="AC4">
-        <v>-0.04645159641320681</v>
+        <v>0.0645663136312809</v>
       </c>
       <c r="AD4">
-        <v>79151.3</v>
+        <v>3</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>33.99351413926314</v>
       </c>
       <c r="AF4">
-        <v>79151.3</v>
+        <v>36.99351413926314</v>
       </c>
       <c r="AG4">
-        <v>67445.7</v>
+        <v>-9.406485860736858</v>
       </c>
       <c r="AH4">
-        <v>0.9934981228653949</v>
+        <v>0.174503046894922</v>
       </c>
       <c r="AI4">
-        <v>0.5816253497777882</v>
+        <v>0.2081871942172878</v>
       </c>
       <c r="AJ4">
-        <v>0.992378284289996</v>
+        <v>-0.05680467565188611</v>
       </c>
       <c r="AK4">
-        <v>0.5422516980112686</v>
+        <v>-0.07164471087855408</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.596</v>
+      </c>
+      <c r="AN4">
+        <v>0.08883624518803673</v>
+      </c>
+      <c r="AP4">
+        <v>-0.2785456280940734</v>
+      </c>
+      <c r="AQ4">
+        <v>-22.98657718120806</v>
       </c>
     </row>
     <row r="5">
@@ -930,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hypothekarbank Lenzburg AG (SWX:HBLN)</t>
+          <t>Schweizerische Nationalbank (SWX:SNBN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -939,10 +981,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0444</v>
+        <v>-0.0194</v>
       </c>
       <c r="E5">
-        <v>-0.0329</v>
+        <v>-0.0199</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -957,85 +999,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>18.5</v>
+        <v>12659.7</v>
       </c>
       <c r="L5">
-        <v>0.1887755102040816</v>
+        <v>0.9654607019202904</v>
       </c>
       <c r="M5">
-        <v>8.668799999999999</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02719196988707653</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4685837837837837</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>8.668799999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02719196988707653</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4685837837837837</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>1348.3</v>
+        <v>12325.2</v>
       </c>
       <c r="V5">
-        <v>4.229297365119197</v>
+        <v>24.13393381633053</v>
       </c>
       <c r="W5">
-        <v>0.03222435115833478</v>
+        <v>0.2223531705397901</v>
       </c>
       <c r="X5">
-        <v>0.07732934722679684</v>
+        <v>3.693205153654952</v>
       </c>
       <c r="Y5">
-        <v>-0.04510499606846206</v>
+        <v>-3.470851983115162</v>
       </c>
       <c r="Z5">
-        <v>0.1866311178823082</v>
+        <v>0.1054230234891559</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04679252837421179</v>
+        <v>0.04788036930927565</v>
       </c>
       <c r="AC5">
-        <v>-0.04679252837421179</v>
+        <v>-0.04788036930927565</v>
       </c>
       <c r="AD5">
-        <v>1215.9</v>
+        <v>197762.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1215.9</v>
+        <v>197762.6</v>
       </c>
       <c r="AG5">
-        <v>-132.3999999999999</v>
+        <v>185437.4</v>
       </c>
       <c r="AH5">
-        <v>0.7922721052974523</v>
+        <v>0.9974242623691641</v>
       </c>
       <c r="AI5">
-        <v>0.6819023049744827</v>
+        <v>0.7283384224771356</v>
       </c>
       <c r="AJ5">
-        <v>-0.7103004291845481</v>
+        <v>0.9972535347228608</v>
       </c>
       <c r="AK5">
-        <v>-0.3045078196872121</v>
+        <v>0.7154206878458953</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1061,13 +1100,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0594</v>
+        <v>0.0454</v>
       </c>
       <c r="E6">
-        <v>0.0418</v>
+        <v>0.00133</v>
       </c>
       <c r="F6">
-        <v>0.00666</v>
+        <v>0.0293</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1076,91 +1115,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.005287510874248636</v>
+        <v>0.005005012930690587</v>
       </c>
       <c r="J6">
-        <v>0.004243093127545525</v>
+        <v>0.004029340306900856</v>
       </c>
       <c r="K6">
-        <v>181.6</v>
+        <v>171.8</v>
       </c>
       <c r="L6">
-        <v>0.3767634854771784</v>
+        <v>0.3335274703940982</v>
       </c>
       <c r="M6">
-        <v>121.45</v>
+        <v>130.8</v>
       </c>
       <c r="N6">
-        <v>0.04976847108962013</v>
+        <v>0.05723537391152145</v>
       </c>
       <c r="O6">
-        <v>0.6687775330396476</v>
+        <v>0.7613504074505237</v>
       </c>
       <c r="P6">
-        <v>118.3</v>
+        <v>129.6</v>
       </c>
       <c r="Q6">
-        <v>0.04847764619104208</v>
+        <v>0.05671027873802126</v>
       </c>
       <c r="R6">
-        <v>0.651431718061674</v>
+        <v>0.7543655413271245</v>
       </c>
       <c r="S6">
-        <v>3.150000000000006</v>
+        <v>1.199999999999989</v>
       </c>
       <c r="T6">
-        <v>0.02593659942363117</v>
+        <v>0.009174311926605418</v>
       </c>
       <c r="U6">
-        <v>508.7</v>
+        <v>670</v>
       </c>
       <c r="V6">
-        <v>0.2084579764783018</v>
+        <v>0.2931781385376099</v>
       </c>
       <c r="W6">
-        <v>0.1529520761391392</v>
+        <v>0.1395159980509989</v>
       </c>
       <c r="X6">
-        <v>0.0563940630796783</v>
+        <v>0.06407590061507314</v>
       </c>
       <c r="Y6">
-        <v>0.09655801305946092</v>
+        <v>0.07544009743592574</v>
       </c>
       <c r="Z6">
-        <v>0.1523312480862137</v>
+        <v>0.161586840408424</v>
       </c>
       <c r="AA6">
-        <v>0.0006463556718650458</v>
+        <v>0.0006510883691224188</v>
       </c>
       <c r="AB6">
-        <v>0.05053247825781781</v>
+        <v>0.0516375942599599</v>
       </c>
       <c r="AC6">
-        <v>-0.04988612258595277</v>
+        <v>-0.05098650589083747</v>
       </c>
       <c r="AD6">
-        <v>2610.3</v>
+        <v>3444.4</v>
       </c>
       <c r="AE6">
-        <v>22.75709879306078</v>
+        <v>18.95958919700639</v>
       </c>
       <c r="AF6">
-        <v>2633.057098793061</v>
+        <v>3463.359589197007</v>
       </c>
       <c r="AG6">
-        <v>2124.357098793061</v>
+        <v>2793.359589197007</v>
       </c>
       <c r="AH6">
-        <v>0.518996996962713</v>
+        <v>0.6024638501304582</v>
       </c>
       <c r="AI6">
-        <v>0.6813523947815107</v>
+        <v>0.7244977128966931</v>
       </c>
       <c r="AJ6">
-        <v>0.4653924824615548</v>
+        <v>0.5500190631281646</v>
       </c>
       <c r="AK6">
-        <v>0.6330485301087829</v>
+        <v>0.6795900768727421</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1169,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>367.6478873239437</v>
+        <v>540.7221350078493</v>
       </c>
       <c r="AP6">
-        <v>299.2052251821213</v>
+        <v>438.5179888849304</v>
       </c>
     </row>
     <row r="7">
@@ -1192,13 +1231,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0356</v>
+        <v>0.0401</v>
       </c>
       <c r="E7">
-        <v>0.123</v>
+        <v>0.7859999999999999</v>
       </c>
       <c r="F7">
-        <v>0.0698</v>
+        <v>0.0604</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1213,216 +1252,91 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>7325</v>
+        <v>30888</v>
       </c>
       <c r="L7">
-        <v>0.2080729462561073</v>
+        <v>0.8367557024435174</v>
       </c>
       <c r="M7">
-        <v>7243</v>
+        <v>5040</v>
       </c>
       <c r="N7">
-        <v>0.1223213184964763</v>
+        <v>0.0502911699083184</v>
       </c>
       <c r="O7">
-        <v>0.9888054607508533</v>
+        <v>0.1631701631701632</v>
       </c>
       <c r="P7">
-        <v>1668</v>
+        <v>1679</v>
       </c>
       <c r="Q7">
-        <v>0.02816953738121254</v>
+        <v>0.01675374489604496</v>
       </c>
       <c r="R7">
-        <v>0.2277133105802048</v>
+        <v>0.05435767935767936</v>
       </c>
       <c r="S7">
-        <v>5575</v>
+        <v>3361</v>
       </c>
       <c r="T7">
-        <v>0.769708684246859</v>
+        <v>0.6668650793650793</v>
       </c>
       <c r="U7">
-        <v>166406</v>
+        <v>281265</v>
       </c>
       <c r="V7">
-        <v>2.810299782648713</v>
+        <v>2.806576568306185</v>
       </c>
       <c r="W7">
-        <v>0.1216393497069031</v>
+        <v>0.5539852213214721</v>
       </c>
       <c r="X7">
-        <v>0.1004397987730437</v>
+        <v>0.1107845855102481</v>
       </c>
       <c r="Y7">
-        <v>0.0211995509338594</v>
+        <v>0.443200635811224</v>
       </c>
       <c r="Z7">
-        <v>0.1525944612770532</v>
+        <v>0.1255744809685639</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05216481483763205</v>
+        <v>0.05243484634545697</v>
       </c>
       <c r="AC7">
-        <v>-0.05216481483763205</v>
+        <v>-0.05243484634545697</v>
       </c>
       <c r="AD7">
-        <v>404611</v>
+        <v>649396</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>404611</v>
+        <v>649396</v>
       </c>
       <c r="AG7">
-        <v>238205</v>
+        <v>368131</v>
       </c>
       <c r="AH7">
-        <v>0.8723375401741911</v>
+        <v>0.8663090418461594</v>
       </c>
       <c r="AI7">
-        <v>0.8782583780662778</v>
+        <v>0.8837796715814228</v>
       </c>
       <c r="AJ7">
-        <v>0.8009100998964755</v>
+        <v>0.7860212312484279</v>
       </c>
       <c r="AK7">
-        <v>0.809419927894499</v>
+        <v>0.811703330988757</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Credit Suisse Group AG (SWX:CSGN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.0474</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>-0.005094480542227136</v>
-      </c>
-      <c r="J8">
-        <v>-0.005094480542227136</v>
-      </c>
-      <c r="K8">
-        <v>-8136</v>
-      </c>
-      <c r="L8">
-        <v>-0.4962397760333754</v>
-      </c>
-      <c r="M8">
-        <v>15875.7</v>
-      </c>
-      <c r="N8">
-        <v>1.338422627829532</v>
-      </c>
-      <c r="O8">
-        <v>-1.951290560471976</v>
-      </c>
-      <c r="P8">
-        <v>284.3</v>
-      </c>
-      <c r="Q8">
-        <v>0.02396830080512583</v>
-      </c>
-      <c r="R8">
-        <v>-0.03494346116027532</v>
-      </c>
-      <c r="S8">
-        <v>15591.4</v>
-      </c>
-      <c r="T8">
-        <v>0.9820921282211178</v>
-      </c>
-      <c r="U8">
-        <v>152012.3</v>
-      </c>
-      <c r="V8">
-        <v>12.81560510896598</v>
-      </c>
-      <c r="W8">
-        <v>-0.1706096737530353</v>
-      </c>
-      <c r="X8">
-        <v>0.1928351920925972</v>
-      </c>
-      <c r="Y8">
-        <v>-0.3634448658456325</v>
-      </c>
-      <c r="Z8">
-        <v>0.1258876783945033</v>
-      </c>
-      <c r="AA8">
-        <v>-0.0006413323280869444</v>
-      </c>
-      <c r="AB8">
-        <v>0.05711740756619302</v>
-      </c>
-      <c r="AC8">
-        <v>-0.05775873989427996</v>
-      </c>
-      <c r="AD8">
-        <v>221757.8</v>
-      </c>
-      <c r="AE8">
-        <v>2469.127684169883</v>
-      </c>
-      <c r="AF8">
-        <v>224226.9276841699</v>
-      </c>
-      <c r="AG8">
-        <v>72214.62768416989</v>
-      </c>
-      <c r="AH8">
-        <v>0.9497582320474095</v>
-      </c>
-      <c r="AI8">
-        <v>0.8349269808422125</v>
-      </c>
-      <c r="AJ8">
-        <v>0.8589195253549561</v>
-      </c>
-      <c r="AK8">
-        <v>0.6196211168296372</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>540.4772117962466</v>
-      </c>
-      <c r="AP8">
-        <v>176.0044545068727</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.01035</v>
+        <v>0.0284</v>
       </c>
       <c r="E2">
-        <v>0.183665</v>
+        <v>0.0301</v>
       </c>
       <c r="F2">
-        <v>0.04485</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G2">
-        <v>0.00202358768814873</v>
+        <v>0.003036842181634256</v>
       </c>
       <c r="H2">
-        <v>0.001496204796449737</v>
+        <v>0.002425327885673774</v>
       </c>
       <c r="I2">
-        <v>0.0020323652797033</v>
+        <v>0.002886946963090552</v>
       </c>
       <c r="J2">
-        <v>0.001633143507512428</v>
+        <v>0.00214544153572085</v>
       </c>
       <c r="K2">
-        <v>43736.47</v>
+        <v>4748.3</v>
       </c>
       <c r="L2">
-        <v>0.8542913341224545</v>
+        <v>0.09842892649183577</v>
       </c>
       <c r="M2">
-        <v>5178.25</v>
+        <v>5638.648</v>
       </c>
       <c r="N2">
-        <v>0.04963851333215746</v>
+        <v>0.05538582431215235</v>
       </c>
       <c r="O2">
-        <v>0.1183966149988785</v>
+        <v>1.187508792620517</v>
       </c>
       <c r="P2">
-        <v>1816.05</v>
+        <v>2386.6</v>
       </c>
       <c r="Q2">
-        <v>0.01740858825604491</v>
+        <v>0.02344246498511394</v>
       </c>
       <c r="R2">
-        <v>0.04152255543257149</v>
+        <v>0.502621991028368</v>
       </c>
       <c r="S2">
-        <v>3362.2</v>
+        <v>3252.048</v>
       </c>
       <c r="T2">
-        <v>0.649292714720224</v>
+        <v>0.5767425099066301</v>
       </c>
       <c r="U2">
-        <v>294541.2</v>
+        <v>264488.5</v>
       </c>
       <c r="V2">
-        <v>2.823461069486729</v>
+        <v>2.597947875729201</v>
       </c>
       <c r="W2">
-        <v>0.1395159980509989</v>
+        <v>0.136294608959757</v>
       </c>
       <c r="X2">
-        <v>0.06407590061507314</v>
+        <v>0.06700894752729586</v>
       </c>
       <c r="Y2">
-        <v>0.07544009743592574</v>
+        <v>0.06928566143246118</v>
       </c>
       <c r="Z2">
-        <v>0.1213952959654896</v>
+        <v>0.1054448078754855</v>
       </c>
       <c r="AA2">
-        <v>0.0006510883691224188</v>
+        <v>0.0005512908884759741</v>
       </c>
       <c r="AB2">
-        <v>0.0516375942599599</v>
+        <v>0.05612828562374023</v>
       </c>
       <c r="AC2">
-        <v>-0.04788036930927565</v>
+        <v>-0.05557699473526425</v>
       </c>
       <c r="AD2">
-        <v>851443.9</v>
+        <v>577870.7</v>
       </c>
       <c r="AE2">
-        <v>52.95310333626954</v>
+        <v>17.2554012412249</v>
       </c>
       <c r="AF2">
-        <v>851496.8531033363</v>
+        <v>577887.9554012412</v>
       </c>
       <c r="AG2">
-        <v>556955.6531033362</v>
+        <v>313399.4554012412</v>
       </c>
       <c r="AH2">
-        <v>0.8908584976562204</v>
+        <v>0.8502170067235546</v>
       </c>
       <c r="AI2">
-        <v>0.8412884461646618</v>
+        <v>0.8664751765897183</v>
       </c>
       <c r="AJ2">
-        <v>0.8422453242998216</v>
+        <v>0.7548044539426024</v>
       </c>
       <c r="AK2">
-        <v>0.7761441539807276</v>
+        <v>0.7787237857550849</v>
       </c>
       <c r="AL2">
-        <v>45.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AM2">
-        <v>41.384</v>
+        <v>60.60999999999999</v>
       </c>
       <c r="AN2">
-        <v>6300.458043510434</v>
+        <v>3691.992716585739</v>
       </c>
       <c r="AO2">
-        <v>2.167755991285403</v>
+        <v>2.098310291858679</v>
       </c>
       <c r="AP2">
-        <v>4121.323465319937</v>
+        <v>2002.29654613622</v>
       </c>
       <c r="AQ2">
-        <v>2.404310844770926</v>
+        <v>2.253753506022109</v>
       </c>
     </row>
     <row r="3">
@@ -724,32 +724,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0155</v>
+      </c>
+      <c r="E3">
+        <v>0.514</v>
+      </c>
+      <c r="F3">
+        <v>0.0182</v>
+      </c>
       <c r="G3">
-        <v>0.1923648983639068</v>
+        <v>0.2828731415331145</v>
       </c>
       <c r="H3">
-        <v>0.1254338125929599</v>
+        <v>0.225912338289245</v>
       </c>
       <c r="I3">
-        <v>0.2126921170054537</v>
+        <v>0.2637574821394091</v>
       </c>
       <c r="J3">
-        <v>0.1063460585027268</v>
+        <v>0.1567216301690076</v>
       </c>
       <c r="K3">
-        <v>9.550000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="L3">
-        <v>0.0236737729300942</v>
+        <v>0.0961575593743966</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0004124947538821271</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.01381526104417671</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -761,76 +770,79 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>234.6</v>
+        <v>105.3</v>
       </c>
       <c r="V3">
-        <v>0.2072804382399717</v>
+        <v>0.06313328137178488</v>
       </c>
       <c r="W3">
-        <v>-7.701612903225807</v>
+        <v>4.184873949579831</v>
       </c>
       <c r="X3">
-        <v>0.05678260670064698</v>
+        <v>0.05964835843587863</v>
       </c>
       <c r="Y3">
-        <v>-7.758395509926454</v>
+        <v>4.125225591143953</v>
       </c>
       <c r="Z3">
-        <v>4.160478547854784</v>
+        <v>0.8418400520156047</v>
       </c>
       <c r="AA3">
-        <v>0.4424504950495048</v>
+        <v>0.1319345452934478</v>
       </c>
       <c r="AB3">
-        <v>0.05812924957302749</v>
+        <v>0.06014208840909959</v>
       </c>
       <c r="AC3">
-        <v>0.3843212454764773</v>
+        <v>0.07179245688434815</v>
       </c>
       <c r="AD3">
-        <v>837.9</v>
+        <v>653.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>837.9</v>
+        <v>653.3</v>
       </c>
       <c r="AG3">
-        <v>603.3</v>
+        <v>548</v>
       </c>
       <c r="AH3">
-        <v>0.4253947301619536</v>
+        <v>0.2814492503877305</v>
       </c>
       <c r="AI3">
-        <v>0.9782837127845884</v>
+        <v>0.8471213692946058</v>
       </c>
       <c r="AJ3">
-        <v>0.3477033024033197</v>
+        <v>0.2473035786813484</v>
       </c>
       <c r="AK3">
-        <v>0.97009165460685</v>
+        <v>0.8229463883465986</v>
       </c>
       <c r="AL3">
-        <v>45.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AM3">
-        <v>41.98</v>
+        <v>60.60999999999999</v>
       </c>
       <c r="AN3">
-        <v>8.82</v>
+        <v>4.343749999999999</v>
       </c>
       <c r="AO3">
-        <v>1.869281045751634</v>
+        <v>2.098310291858679</v>
       </c>
       <c r="AP3">
-        <v>6.350526315789473</v>
+        <v>3.643617021276595</v>
       </c>
       <c r="AQ3">
-        <v>2.043830395426394</v>
+        <v>2.253753506022109</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orell Füssli AG (SWX:OFN)</t>
+          <t>Cembra Money Bank AG (SWX:CMBN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,118 +862,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0459</v>
+        <v>0.0284</v>
       </c>
       <c r="E4">
-        <v>0.366</v>
+        <v>0.00796</v>
+      </c>
+      <c r="F4">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G4">
-        <v>0.1035444046196734</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.1035444046196734</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.06241058212722968</v>
+        <v>0.005172325100300426</v>
       </c>
       <c r="J4">
-        <v>0.04760420953980415</v>
+        <v>0.004163373791497428</v>
       </c>
       <c r="K4">
-        <v>7.42</v>
+        <v>179.5</v>
       </c>
       <c r="L4">
-        <v>0.0295499800876145</v>
+        <v>0.3478682170542636</v>
       </c>
       <c r="M4">
-        <v>7.45</v>
+        <v>132.96</v>
       </c>
       <c r="N4">
-        <v>0.04257142857142857</v>
+        <v>0.05011684885035809</v>
       </c>
       <c r="O4">
-        <v>1.004043126684636</v>
+        <v>0.7407242339832869</v>
       </c>
       <c r="P4">
-        <v>7.45</v>
+        <v>130.6</v>
       </c>
       <c r="Q4">
-        <v>0.04257142857142857</v>
+        <v>0.04922728986053524</v>
       </c>
       <c r="R4">
-        <v>1.004043126684636</v>
+        <v>0.7275766016713091</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.360000000000014</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.0177496991576415</v>
       </c>
       <c r="U4">
-        <v>46.4</v>
+        <v>1091.2</v>
       </c>
       <c r="V4">
-        <v>0.2651428571428571</v>
+        <v>0.4113079532604599</v>
       </c>
       <c r="W4">
-        <v>0.05638297872340426</v>
+        <v>0.136294608959757</v>
       </c>
       <c r="X4">
-        <v>0.05180605746985757</v>
+        <v>0.06700894752729586</v>
       </c>
       <c r="Y4">
-        <v>0.004576921253546695</v>
+        <v>0.06928566143246118</v>
       </c>
       <c r="Z4">
-        <v>2.395683438934884</v>
+        <v>0.1324144590624646</v>
       </c>
       <c r="AA4">
-        <v>0.1140446164180948</v>
+        <v>0.0005512908884759741</v>
       </c>
       <c r="AB4">
-        <v>0.04947830278681391</v>
+        <v>0.05612828562374023</v>
       </c>
       <c r="AC4">
-        <v>0.0645663136312809</v>
+        <v>-0.05557699473526425</v>
       </c>
       <c r="AD4">
-        <v>3</v>
+        <v>3225.4</v>
       </c>
       <c r="AE4">
-        <v>33.99351413926314</v>
+        <v>17.2554012412249</v>
       </c>
       <c r="AF4">
-        <v>36.99351413926314</v>
+        <v>3242.655401241225</v>
       </c>
       <c r="AG4">
-        <v>-9.406485860736858</v>
+        <v>2151.455401241225</v>
       </c>
       <c r="AH4">
-        <v>0.174503046894922</v>
+        <v>0.5500076209607742</v>
       </c>
       <c r="AI4">
-        <v>0.2081871942172878</v>
+        <v>0.7066216857030575</v>
       </c>
       <c r="AJ4">
-        <v>-0.05680467565188611</v>
+        <v>0.4478042195345177</v>
       </c>
       <c r="AK4">
-        <v>-0.07164471087855408</v>
+        <v>0.6150960128537725</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.596</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.08883624518803673</v>
+        <v>527.0261437908497</v>
       </c>
       <c r="AP4">
-        <v>-0.2785456280940734</v>
-      </c>
-      <c r="AQ4">
-        <v>-22.98657718120806</v>
+        <v>351.5450002028144</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Schweizerische Nationalbank (SWX:SNBN)</t>
+          <t>UBS Group AG (SWX:UBSG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,10 +993,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0194</v>
+        <v>0.103</v>
       </c>
       <c r="E5">
-        <v>-0.0199</v>
+        <v>0.0301</v>
+      </c>
+      <c r="F5">
+        <v>0.294</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -999,343 +1014,90 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>12659.7</v>
+        <v>4519</v>
       </c>
       <c r="L5">
-        <v>0.9654607019202904</v>
+        <v>0.09572732857415214</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>5505</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05646976277570682</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>1.218189865014384</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>2256</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02314183193860029</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.4992254923655676</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3249</v>
+      </c>
+      <c r="T5">
+        <v>0.5901907356948229</v>
       </c>
       <c r="U5">
-        <v>12325.2</v>
+        <v>263292</v>
       </c>
       <c r="V5">
-        <v>24.13393381633053</v>
+        <v>2.700824120025686</v>
       </c>
       <c r="W5">
-        <v>0.2223531705397901</v>
+        <v>0.05325492599226925</v>
       </c>
       <c r="X5">
-        <v>3.693205153654952</v>
+        <v>0.1083567888656401</v>
       </c>
       <c r="Y5">
-        <v>-3.470851983115162</v>
+        <v>-0.05510186287337081</v>
       </c>
       <c r="Z5">
-        <v>0.1054230234891559</v>
+        <v>0.1042127036758229</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04788036930927565</v>
+        <v>0.05610119833954007</v>
       </c>
       <c r="AC5">
-        <v>-0.04788036930927565</v>
+        <v>-0.05610119833954007</v>
       </c>
       <c r="AD5">
-        <v>197762.6</v>
+        <v>573992</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>197762.6</v>
+        <v>573992</v>
       </c>
       <c r="AG5">
-        <v>185437.4</v>
+        <v>310700</v>
       </c>
       <c r="AH5">
-        <v>0.9974242623691641</v>
+        <v>0.854819027524067</v>
       </c>
       <c r="AI5">
-        <v>0.7283384224771356</v>
+        <v>0.8676065364634111</v>
       </c>
       <c r="AJ5">
-        <v>0.9972535347228608</v>
+        <v>0.761172975640015</v>
       </c>
       <c r="AK5">
-        <v>0.7154206878458953</v>
+        <v>0.7800868213784463</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cembra Money Bank AG (SWX:CMBN)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0454</v>
-      </c>
-      <c r="E6">
-        <v>0.00133</v>
-      </c>
-      <c r="F6">
-        <v>0.0293</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0.005005012930690587</v>
-      </c>
-      <c r="J6">
-        <v>0.004029340306900856</v>
-      </c>
-      <c r="K6">
-        <v>171.8</v>
-      </c>
-      <c r="L6">
-        <v>0.3335274703940982</v>
-      </c>
-      <c r="M6">
-        <v>130.8</v>
-      </c>
-      <c r="N6">
-        <v>0.05723537391152145</v>
-      </c>
-      <c r="O6">
-        <v>0.7613504074505237</v>
-      </c>
-      <c r="P6">
-        <v>129.6</v>
-      </c>
-      <c r="Q6">
-        <v>0.05671027873802126</v>
-      </c>
-      <c r="R6">
-        <v>0.7543655413271245</v>
-      </c>
-      <c r="S6">
-        <v>1.199999999999989</v>
-      </c>
-      <c r="T6">
-        <v>0.009174311926605418</v>
-      </c>
-      <c r="U6">
-        <v>670</v>
-      </c>
-      <c r="V6">
-        <v>0.2931781385376099</v>
-      </c>
-      <c r="W6">
-        <v>0.1395159980509989</v>
-      </c>
-      <c r="X6">
-        <v>0.06407590061507314</v>
-      </c>
-      <c r="Y6">
-        <v>0.07544009743592574</v>
-      </c>
-      <c r="Z6">
-        <v>0.161586840408424</v>
-      </c>
-      <c r="AA6">
-        <v>0.0006510883691224188</v>
-      </c>
-      <c r="AB6">
-        <v>0.0516375942599599</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05098650589083747</v>
-      </c>
-      <c r="AD6">
-        <v>3444.4</v>
-      </c>
-      <c r="AE6">
-        <v>18.95958919700639</v>
-      </c>
-      <c r="AF6">
-        <v>3463.359589197007</v>
-      </c>
-      <c r="AG6">
-        <v>2793.359589197007</v>
-      </c>
-      <c r="AH6">
-        <v>0.6024638501304582</v>
-      </c>
-      <c r="AI6">
-        <v>0.7244977128966931</v>
-      </c>
-      <c r="AJ6">
-        <v>0.5500190631281646</v>
-      </c>
-      <c r="AK6">
-        <v>0.6795900768727421</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>540.7221350078493</v>
-      </c>
-      <c r="AP6">
-        <v>438.5179888849304</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>UBS Group AG (SWX:UBSG)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0401</v>
-      </c>
-      <c r="E7">
-        <v>0.7859999999999999</v>
-      </c>
-      <c r="F7">
-        <v>0.0604</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>30888</v>
-      </c>
-      <c r="L7">
-        <v>0.8367557024435174</v>
-      </c>
-      <c r="M7">
-        <v>5040</v>
-      </c>
-      <c r="N7">
-        <v>0.0502911699083184</v>
-      </c>
-      <c r="O7">
-        <v>0.1631701631701632</v>
-      </c>
-      <c r="P7">
-        <v>1679</v>
-      </c>
-      <c r="Q7">
-        <v>0.01675374489604496</v>
-      </c>
-      <c r="R7">
-        <v>0.05435767935767936</v>
-      </c>
-      <c r="S7">
-        <v>3361</v>
-      </c>
-      <c r="T7">
-        <v>0.6668650793650793</v>
-      </c>
-      <c r="U7">
-        <v>281265</v>
-      </c>
-      <c r="V7">
-        <v>2.806576568306185</v>
-      </c>
-      <c r="W7">
-        <v>0.5539852213214721</v>
-      </c>
-      <c r="X7">
-        <v>0.1107845855102481</v>
-      </c>
-      <c r="Y7">
-        <v>0.443200635811224</v>
-      </c>
-      <c r="Z7">
-        <v>0.1255744809685639</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.05243484634545697</v>
-      </c>
-      <c r="AC7">
-        <v>-0.05243484634545697</v>
-      </c>
-      <c r="AD7">
-        <v>649396</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>649396</v>
-      </c>
-      <c r="AG7">
-        <v>368131</v>
-      </c>
-      <c r="AH7">
-        <v>0.8663090418461594</v>
-      </c>
-      <c r="AI7">
-        <v>0.8837796715814228</v>
-      </c>
-      <c r="AJ7">
-        <v>0.7860212312484279</v>
-      </c>
-      <c r="AK7">
-        <v>0.811703330988757</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/switzerland/switzerland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0284</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0301</v>
+        <v>0.09854999999999998</v>
       </c>
       <c r="F2">
         <v>0.07000000000000001</v>
       </c>
       <c r="G2">
-        <v>0.003036842181634256</v>
+        <v>0.001573429765424713</v>
       </c>
       <c r="H2">
-        <v>0.002425327885673774</v>
+        <v>0.001256595785356256</v>
       </c>
       <c r="I2">
-        <v>0.002886946963090552</v>
+        <v>0.001495766987958752</v>
       </c>
       <c r="J2">
-        <v>0.00214544153572085</v>
+        <v>0.001207628856093531</v>
       </c>
       <c r="K2">
-        <v>4748.3</v>
+        <v>49145.7</v>
       </c>
       <c r="L2">
-        <v>0.09842892649183577</v>
+        <v>0.5278314486186576</v>
       </c>
       <c r="M2">
         <v>5638.648</v>
       </c>
       <c r="N2">
-        <v>0.05538582431215235</v>
+        <v>0.05519498584065773</v>
       </c>
       <c r="O2">
-        <v>1.187508792620517</v>
+        <v>0.1147332930449663</v>
       </c>
       <c r="P2">
         <v>2386.6</v>
       </c>
       <c r="Q2">
-        <v>0.02344246498511394</v>
+        <v>0.02336169117265588</v>
       </c>
       <c r="R2">
-        <v>0.502621991028368</v>
+        <v>0.04856172564435952</v>
       </c>
       <c r="S2">
         <v>3252.048</v>
@@ -639,55 +639,55 @@
         <v>0.5767425099066301</v>
       </c>
       <c r="U2">
-        <v>264488.5</v>
+        <v>276656</v>
       </c>
       <c r="V2">
-        <v>2.597947875729201</v>
+        <v>2.708100240116603</v>
       </c>
       <c r="W2">
-        <v>0.136294608959757</v>
+        <v>0.3180445816783435</v>
       </c>
       <c r="X2">
-        <v>0.06700894752729586</v>
+        <v>0.0876559412360457</v>
       </c>
       <c r="Y2">
-        <v>0.06928566143246118</v>
+        <v>0.2303886404422978</v>
       </c>
       <c r="Z2">
-        <v>0.1054448078754855</v>
+        <v>0.118987863614461</v>
       </c>
       <c r="AA2">
-        <v>0.0005512908884759741</v>
+        <v>0.000275645444237987</v>
       </c>
       <c r="AB2">
-        <v>0.05612828562374023</v>
+        <v>0.05610875457631698</v>
       </c>
       <c r="AC2">
-        <v>-0.05557699473526425</v>
+        <v>-0.05433539417683494</v>
       </c>
       <c r="AD2">
-        <v>577870.7</v>
+        <v>748611.4</v>
       </c>
       <c r="AE2">
         <v>17.2554012412249</v>
       </c>
       <c r="AF2">
-        <v>577887.9554012412</v>
+        <v>748628.6554012413</v>
       </c>
       <c r="AG2">
-        <v>313399.4554012412</v>
+        <v>471972.6554012413</v>
       </c>
       <c r="AH2">
-        <v>0.8502170067235546</v>
+        <v>0.8799245200913679</v>
       </c>
       <c r="AI2">
-        <v>0.8664751765897183</v>
+        <v>0.7713520262799685</v>
       </c>
       <c r="AJ2">
-        <v>0.7548044539426024</v>
+        <v>0.8220638900158925</v>
       </c>
       <c r="AK2">
-        <v>0.7787237857550849</v>
+        <v>0.6801887254454076</v>
       </c>
       <c r="AL2">
         <v>65.09999999999999</v>
@@ -696,13 +696,13 @@
         <v>60.60999999999999</v>
       </c>
       <c r="AN2">
-        <v>3691.992716585739</v>
+        <v>4782.848198313314</v>
       </c>
       <c r="AO2">
         <v>2.098310291858679</v>
       </c>
       <c r="AP2">
-        <v>2002.29654613622</v>
+        <v>3015.414358556358</v>
       </c>
       <c r="AQ2">
         <v>2.253753506022109</v>
@@ -785,10 +785,10 @@
         <v>4.184873949579831</v>
       </c>
       <c r="X3">
-        <v>0.05964835843587863</v>
+        <v>0.05963945517266926</v>
       </c>
       <c r="Y3">
-        <v>4.125225591143953</v>
+        <v>4.125234494407162</v>
       </c>
       <c r="Z3">
         <v>0.8418400520156047</v>
@@ -797,10 +797,10 @@
         <v>0.1319345452934478</v>
       </c>
       <c r="AB3">
-        <v>0.06014208840909959</v>
+        <v>0.0601356909626465</v>
       </c>
       <c r="AC3">
-        <v>0.07179245688434815</v>
+        <v>0.07179885433080124</v>
       </c>
       <c r="AD3">
         <v>653.3</v>
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cembra Money Bank AG (SWX:CMBN)</t>
+          <t>Schweizerische Nationalbank (SWX:SNBN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,13 +862,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0284</v>
+        <v>0.165</v>
       </c>
       <c r="E4">
-        <v>0.00796</v>
-      </c>
-      <c r="F4">
-        <v>0.07000000000000001</v>
+        <v>0.167</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -877,103 +874,94 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.005172325100300426</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.004163373791497428</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>179.5</v>
+        <v>44397.4</v>
       </c>
       <c r="L4">
-        <v>0.3478682170542636</v>
+        <v>0.9895158666125818</v>
       </c>
       <c r="M4">
-        <v>132.96</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.05011684885035809</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.7407242339832869</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>130.6</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04922728986053524</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.7275766016713091</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>2.360000000000014</v>
-      </c>
-      <c r="T4">
-        <v>0.0177496991576415</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1091.2</v>
+        <v>12167.5</v>
       </c>
       <c r="V4">
-        <v>0.4113079532604599</v>
+        <v>34.56676136363637</v>
       </c>
       <c r="W4">
-        <v>0.136294608959757</v>
+        <v>0.4997945543969299</v>
       </c>
       <c r="X4">
-        <v>0.06700894752729586</v>
+        <v>4.352044913718778</v>
       </c>
       <c r="Y4">
-        <v>0.06928566143246118</v>
+        <v>-3.852250359321848</v>
       </c>
       <c r="Z4">
-        <v>0.1324144590624646</v>
+        <v>0.1380518807606487</v>
       </c>
       <c r="AA4">
-        <v>0.0005512908884759741</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05612828562374023</v>
+        <v>0.05309992947489284</v>
       </c>
       <c r="AC4">
-        <v>-0.05557699473526425</v>
+        <v>-0.05309992947489284</v>
       </c>
       <c r="AD4">
-        <v>3225.4</v>
+        <v>170740.7</v>
       </c>
       <c r="AE4">
-        <v>17.2554012412249</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>3242.655401241225</v>
+        <v>170740.7</v>
       </c>
       <c r="AG4">
-        <v>2151.455401241225</v>
+        <v>158573.2</v>
       </c>
       <c r="AH4">
-        <v>0.5500076209607742</v>
+        <v>0.9979426357758104</v>
       </c>
       <c r="AI4">
-        <v>0.7066216857030575</v>
+        <v>0.5623875781168427</v>
       </c>
       <c r="AJ4">
-        <v>0.4478042195345177</v>
+        <v>0.9977851215540393</v>
       </c>
       <c r="AK4">
-        <v>0.6150960128537725</v>
+        <v>0.5441169507007119</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>527.0261437908497</v>
-      </c>
-      <c r="AP4">
-        <v>351.5450002028144</v>
       </c>
     </row>
     <row r="5">
@@ -984,120 +972,251 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Cembra Money Bank AG (SWX:CMBN)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0284</v>
+      </c>
+      <c r="E5">
+        <v>0.00796</v>
+      </c>
+      <c r="F5">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0.005172325100300426</v>
+      </c>
+      <c r="J5">
+        <v>0.004163373791497428</v>
+      </c>
+      <c r="K5">
+        <v>179.5</v>
+      </c>
+      <c r="L5">
+        <v>0.3478682170542636</v>
+      </c>
+      <c r="M5">
+        <v>132.96</v>
+      </c>
+      <c r="N5">
+        <v>0.05011684885035809</v>
+      </c>
+      <c r="O5">
+        <v>0.7407242339832869</v>
+      </c>
+      <c r="P5">
+        <v>130.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.04922728986053524</v>
+      </c>
+      <c r="R5">
+        <v>0.7275766016713091</v>
+      </c>
+      <c r="S5">
+        <v>2.360000000000014</v>
+      </c>
+      <c r="T5">
+        <v>0.0177496991576415</v>
+      </c>
+      <c r="U5">
+        <v>1091.2</v>
+      </c>
+      <c r="V5">
+        <v>0.4113079532604599</v>
+      </c>
+      <c r="W5">
+        <v>0.136294608959757</v>
+      </c>
+      <c r="X5">
+        <v>0.06699531205973461</v>
+      </c>
+      <c r="Y5">
+        <v>0.06929929690002243</v>
+      </c>
+      <c r="Z5">
+        <v>0.1324144590624646</v>
+      </c>
+      <c r="AA5">
+        <v>0.0005512908884759741</v>
+      </c>
+      <c r="AB5">
+        <v>0.05612214976725303</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05557085887877705</v>
+      </c>
+      <c r="AD5">
+        <v>3225.4</v>
+      </c>
+      <c r="AE5">
+        <v>17.2554012412249</v>
+      </c>
+      <c r="AF5">
+        <v>3242.655401241225</v>
+      </c>
+      <c r="AG5">
+        <v>2151.455401241225</v>
+      </c>
+      <c r="AH5">
+        <v>0.5500076209607742</v>
+      </c>
+      <c r="AI5">
+        <v>0.7066216857030575</v>
+      </c>
+      <c r="AJ5">
+        <v>0.4478042195345177</v>
+      </c>
+      <c r="AK5">
+        <v>0.6150960128537725</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>527.0261437908497</v>
+      </c>
+      <c r="AP5">
+        <v>351.5450002028144</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>UBS Group AG (SWX:UBSG)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>0.103</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>0.0301</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>0.294</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>4519</v>
       </c>
-      <c r="L5">
+      <c r="L6">
         <v>0.09572732857415214</v>
       </c>
-      <c r="M5">
+      <c r="M6">
         <v>5505</v>
       </c>
-      <c r="N5">
+      <c r="N6">
         <v>0.05646976277570682</v>
       </c>
-      <c r="O5">
+      <c r="O6">
         <v>1.218189865014384</v>
       </c>
-      <c r="P5">
+      <c r="P6">
         <v>2256</v>
       </c>
-      <c r="Q5">
+      <c r="Q6">
         <v>0.02314183193860029</v>
       </c>
-      <c r="R5">
+      <c r="R6">
         <v>0.4992254923655676</v>
       </c>
-      <c r="S5">
+      <c r="S6">
         <v>3249</v>
       </c>
-      <c r="T5">
+      <c r="T6">
         <v>0.5901907356948229</v>
       </c>
-      <c r="U5">
+      <c r="U6">
         <v>263292</v>
       </c>
-      <c r="V5">
+      <c r="V6">
         <v>2.700824120025686</v>
       </c>
-      <c r="W5">
+      <c r="W6">
         <v>0.05325492599226925</v>
       </c>
-      <c r="X5">
-        <v>0.1083567888656401</v>
-      </c>
-      <c r="Y5">
-        <v>-0.05510186287337081</v>
-      </c>
-      <c r="Z5">
+      <c r="X6">
+        <v>0.1083165704123568</v>
+      </c>
+      <c r="Y6">
+        <v>-0.05506164442008753</v>
+      </c>
+      <c r="Z6">
         <v>0.1042127036758229</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05610119833954007</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05610119833954007</v>
-      </c>
-      <c r="AD5">
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.05609535938538092</v>
+      </c>
+      <c r="AC6">
+        <v>-0.05609535938538092</v>
+      </c>
+      <c r="AD6">
         <v>573992</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
         <v>573992</v>
       </c>
-      <c r="AG5">
+      <c r="AG6">
         <v>310700</v>
       </c>
-      <c r="AH5">
+      <c r="AH6">
         <v>0.854819027524067</v>
       </c>
-      <c r="AI5">
+      <c r="AI6">
         <v>0.8676065364634111</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ6">
         <v>0.761172975640015</v>
       </c>
-      <c r="AK5">
+      <c r="AK6">
         <v>0.7800868213784463</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>0</v>
       </c>
     </row>
